--- a/runup_numerical.xlsx
+++ b/runup_numerical.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NTU\manuscript\20250914WaterWavesNwaveNum\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE5E0B5-27DD-461A-8F65-7EF60CA5F6AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6BE4964-35EA-46AA-813E-6C7FF07E2ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-100" yWindow="-100" windowWidth="21467" windowHeight="11565" tabRatio="775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -440,34 +440,6 @@
     <t>S24n</t>
   </si>
   <si>
-    <t>Numerical simulation results of solitary wave runup on a 1:10 slope. Toe of slope is located at x=13.5 m. Still water depth h=0.2 m.</t>
-  </si>
-  <si>
-    <t>Numerical simulation results of solitary wave runup on a 1:10 slope. Toe of slope is located at x=7 m. Still water depth h=0.2 m.</t>
-  </si>
-  <si>
-    <t>Numerical simulation results of solitary wave runup on a 1:20 slope. Toe of slope is located at x=13.5 m. Still water depth h=0.2 m.</t>
-  </si>
-  <si>
-    <t>Numerical simulation results of solitary wave runup on a 1:40 slope. Toe of slope is located at x=13.5 m. Still water depth h=0.2 m.</t>
-  </si>
-  <si>
-    <t>Numerical simulation results of LDN runup on a 1:10 slope. Toe of slope is located at x=13.5 m. Empty case: did not run simulation. Still water depth h=0.2 m.</t>
-  </si>
-  <si>
-    <t>Numerical simulation results of LDN runup on a 1:10 slope. Toe of slope is located at x=7 m. Empty case: did not run simulation. Still water depth h=0.2 m.</t>
-  </si>
-  <si>
-    <t>Numerical simulation results of LDN runup on a 1:20 slope. Toe of slope is located at x=13.5 m. Empty case: did not run simulation. Still water depth h=0.2 m.</t>
-  </si>
-  <si>
-    <t>Numerical simulation results of LDN runup on a 1:40 slope. Toe of slope is located at x=13.5 m. Empty case: did not run simulation. Still water depth h=0.2 m.</t>
-  </si>
-  <si>
-    <t>Wavemaking parameters for the LDNs using a piston-type wavemaker. The LDN cases considered are the same as those used in Lo et al. (2024, Coastal Engineering, doi:10.1016/j.coastaleng.2024.104479). The LDN wavemaking method is proposed by Lima et al. (2019, Coastal Engineering, doi:10.1016/j.coastaleng.
-2019.02.012). Still water depth h=0.2 m.</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -495,6 +467,34 @@
 The spreadsheet tabulates the numerical simulation results for the 350 cases considered in the paper.
 Please direct all questions related to this study to Peter H.-Y. Lo: peterhylo@ntu.edu.tw</t>
     </r>
+  </si>
+  <si>
+    <t>Numerical simulation results of solitary wave runup on a 1:10 slope. Toe of slope is located at x=13.5 m. Still water depth h=0.23 m.</t>
+  </si>
+  <si>
+    <t>Numerical simulation results of solitary wave runup on a 1:10 slope. Toe of slope is located at x=7 m. Still water depth h=0.23 m.</t>
+  </si>
+  <si>
+    <t>Numerical simulation results of solitary wave runup on a 1:20 slope. Toe of slope is located at x=13.5 m. Still water depth h=0.23 m.</t>
+  </si>
+  <si>
+    <t>Numerical simulation results of solitary wave runup on a 1:40 slope. Toe of slope is located at x=13.5 m. Still water depth h=0.23 m.</t>
+  </si>
+  <si>
+    <t>Wavemaking parameters for the LDNs using a piston-type wavemaker. The LDN cases considered are the same as those used in Lo et al. (2024, Coastal Engineering, doi:10.1016/j.coastaleng.2024.104479). The LDN wavemaking method is proposed by Lima et al. (2019, Coastal Engineering, doi:10.1016/j.coastaleng.
+2019.02.012). Still water depth h=0.23 m.</t>
+  </si>
+  <si>
+    <t>Numerical simulation results of LDN runup on a 1:10 slope. Toe of slope is located at x=13.5 m. Empty case: did not run simulation. Still water depth h=0.23 m.</t>
+  </si>
+  <si>
+    <t>Numerical simulation results of LDN runup on a 1:10 slope. Toe of slope is located at x=7 m. Empty case: did not run simulation. Still water depth h=0.23 m.</t>
+  </si>
+  <si>
+    <t>Numerical simulation results of LDN runup on a 1:20 slope. Toe of slope is located at x=13.5 m. Empty case: did not run simulation. Still water depth h=0.23 m.</t>
+  </si>
+  <si>
+    <t>Numerical simulation results of LDN runup on a 1:40 slope. Toe of slope is located at x=13.5 m. Empty case: did not run simulation. Still water depth h=0.23 m.</t>
   </si>
 </sst>
 </file>
@@ -611,10 +611,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -904,8 +904,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="199.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
-        <v>140</v>
+      <c r="A1" s="18" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -924,16 +924,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="A1" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
     </row>
     <row r="2" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13"/>
@@ -3020,15 +3020,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="A1" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
@@ -3668,15 +3668,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="A1" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
       <c r="H1" s="17"/>
     </row>
     <row r="2" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
@@ -4320,15 +4320,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="A1" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
       <c r="H1" s="15"/>
     </row>
     <row r="2" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
@@ -4969,15 +4969,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="A1" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
       <c r="H1" s="15"/>
     </row>
     <row r="2" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
@@ -5617,13 +5617,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
+      <c r="A1" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
       <c r="F1" s="14"/>
       <c r="G1" s="14"/>
       <c r="H1" s="14"/>
@@ -7428,16 +7428,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="A1" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
     </row>
     <row r="2" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13"/>
@@ -9526,16 +9526,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="A1" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
     </row>
     <row r="2" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13"/>
@@ -11593,16 +11593,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="A1" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
     </row>
     <row r="2" spans="1:8" s="2" customFormat="1" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13"/>

--- a/runup_numerical.xlsx
+++ b/runup_numerical.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NTU\manuscript\20250914WaterWavesNwaveNum\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6BE4964-35EA-46AA-813E-6C7FF07E2ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA0D3FF7-C543-4503-A23A-09AD17121420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-100" yWindow="-100" windowWidth="21467" windowHeight="11565" tabRatio="775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -440,6 +440,34 @@
     <t>S24n</t>
   </si>
   <si>
+    <t>Numerical simulation results of solitary wave runup on a 1:10 slope. Toe of slope is located at x=13.5 m. Still water depth h=0.23 m.</t>
+  </si>
+  <si>
+    <t>Numerical simulation results of solitary wave runup on a 1:10 slope. Toe of slope is located at x=7 m. Still water depth h=0.23 m.</t>
+  </si>
+  <si>
+    <t>Numerical simulation results of solitary wave runup on a 1:20 slope. Toe of slope is located at x=13.5 m. Still water depth h=0.23 m.</t>
+  </si>
+  <si>
+    <t>Numerical simulation results of solitary wave runup on a 1:40 slope. Toe of slope is located at x=13.5 m. Still water depth h=0.23 m.</t>
+  </si>
+  <si>
+    <t>Wavemaking parameters for the LDNs using a piston-type wavemaker. The LDN cases considered are the same as those used in Lo et al. (2024, Coastal Engineering, doi:10.1016/j.coastaleng.2024.104479). The LDN wavemaking method is proposed by Lima et al. (2019, Coastal Engineering, doi:10.1016/j.coastaleng.
+2019.02.012). Still water depth h=0.23 m.</t>
+  </si>
+  <si>
+    <t>Numerical simulation results of LDN runup on a 1:10 slope. Toe of slope is located at x=13.5 m. Empty case: did not run simulation. Still water depth h=0.23 m.</t>
+  </si>
+  <si>
+    <t>Numerical simulation results of LDN runup on a 1:10 slope. Toe of slope is located at x=7 m. Empty case: did not run simulation. Still water depth h=0.23 m.</t>
+  </si>
+  <si>
+    <t>Numerical simulation results of LDN runup on a 1:20 slope. Toe of slope is located at x=13.5 m. Empty case: did not run simulation. Still water depth h=0.23 m.</t>
+  </si>
+  <si>
+    <t>Numerical simulation results of LDN runup on a 1:40 slope. Toe of slope is located at x=13.5 m. Empty case: did not run simulation. Still water depth h=0.23 m.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -448,7 +476,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">[FILES LAST UPDATED ON 2026/03/21]
+      <t xml:space="preserve">[FILES LAST UPDATED ON 2026/07/17]
 </t>
     </r>
     <r>
@@ -462,39 +490,11 @@
       <t xml:space="preserve">
 This is the supplementary material for the paper:
 Numerical investigation of the runup of leading-depression N-waves using a two-model approach
-by Peter H.-Y. Lo and Pin-Chen Ko,
-submitted to Water Waves for review on 2026/03/21.
+by Peter H.-Y. Lo and Pin-Chen Ko, Water Waves (2026). 
+https://doi.org/10.1007/s42286-026-00143-y
 The spreadsheet tabulates the numerical simulation results for the 350 cases considered in the paper.
 Please direct all questions related to this study to Peter H.-Y. Lo: peterhylo@ntu.edu.tw</t>
     </r>
-  </si>
-  <si>
-    <t>Numerical simulation results of solitary wave runup on a 1:10 slope. Toe of slope is located at x=13.5 m. Still water depth h=0.23 m.</t>
-  </si>
-  <si>
-    <t>Numerical simulation results of solitary wave runup on a 1:10 slope. Toe of slope is located at x=7 m. Still water depth h=0.23 m.</t>
-  </si>
-  <si>
-    <t>Numerical simulation results of solitary wave runup on a 1:20 slope. Toe of slope is located at x=13.5 m. Still water depth h=0.23 m.</t>
-  </si>
-  <si>
-    <t>Numerical simulation results of solitary wave runup on a 1:40 slope. Toe of slope is located at x=13.5 m. Still water depth h=0.23 m.</t>
-  </si>
-  <si>
-    <t>Wavemaking parameters for the LDNs using a piston-type wavemaker. The LDN cases considered are the same as those used in Lo et al. (2024, Coastal Engineering, doi:10.1016/j.coastaleng.2024.104479). The LDN wavemaking method is proposed by Lima et al. (2019, Coastal Engineering, doi:10.1016/j.coastaleng.
-2019.02.012). Still water depth h=0.23 m.</t>
-  </si>
-  <si>
-    <t>Numerical simulation results of LDN runup on a 1:10 slope. Toe of slope is located at x=13.5 m. Empty case: did not run simulation. Still water depth h=0.23 m.</t>
-  </si>
-  <si>
-    <t>Numerical simulation results of LDN runup on a 1:10 slope. Toe of slope is located at x=7 m. Empty case: did not run simulation. Still water depth h=0.23 m.</t>
-  </si>
-  <si>
-    <t>Numerical simulation results of LDN runup on a 1:20 slope. Toe of slope is located at x=13.5 m. Empty case: did not run simulation. Still water depth h=0.23 m.</t>
-  </si>
-  <si>
-    <t>Numerical simulation results of LDN runup on a 1:40 slope. Toe of slope is located at x=13.5 m. Empty case: did not run simulation. Still water depth h=0.23 m.</t>
   </si>
 </sst>
 </file>
@@ -905,7 +905,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="199.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -925,7 +925,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -3021,7 +3021,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -3669,7 +3669,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -4321,7 +4321,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -4970,7 +4970,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -5618,7 +5618,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -7429,7 +7429,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -9527,7 +9527,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -11594,7 +11594,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
